--- a/qa-docs/test-cases/API/API_VerseByVerse_Notes_Test_Cases.xlsx
+++ b/qa-docs/test-cases/API/API_VerseByVerse_Notes_Test_Cases.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\versebyverse-quality-engineering\qa-docs\test-cases\API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4927BBEF-154D-4630-8EE0-F4EC3D71784B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A604EE1F-83AA-4109-8475-BA29C222D810}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="364" uniqueCount="201">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -55,18 +55,12 @@
     <t>Test Type</t>
   </si>
   <si>
-    <t>Status</t>
-  </si>
-  <si>
     <t>High</t>
   </si>
   <si>
     <t>Functional</t>
   </si>
   <si>
-    <t>Not Run</t>
-  </si>
-  <si>
     <t>Validation</t>
   </si>
   <si>
@@ -629,6 +623,9 @@
   </si>
   <si>
     <t>VerseByVerse - API Notes Test Cases</t>
+  </si>
+  <si>
+    <t>Passed</t>
   </si>
 </sst>
 </file>
@@ -1023,7 +1020,7 @@
   <sheetData>
     <row r="1" spans="1:11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -1068,1127 +1065,1127 @@
         <v>9</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>10</v>
+        <v>200</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
       </c>
-      <c r="B3" t="s">
+      <c r="D3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" t="s">
+      <c r="E3" t="s">
         <v>22</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F3" t="s">
         <v>23</v>
       </c>
-      <c r="E3" t="s">
+      <c r="G3" t="s">
         <v>24</v>
       </c>
-      <c r="F3" t="s">
+      <c r="H3" t="s">
         <v>25</v>
       </c>
-      <c r="G3" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" t="s">
-        <v>27</v>
-      </c>
       <c r="I3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" t="s">
         <v>28</v>
       </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="E4" t="s">
+      <c r="G4" t="s">
         <v>30</v>
       </c>
-      <c r="F4" t="s">
-        <v>31</v>
-      </c>
-      <c r="G4" t="s">
-        <v>32</v>
-      </c>
       <c r="H4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="I4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E5" t="s">
         <v>33</v>
       </c>
-      <c r="B5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="F5" t="s">
         <v>34</v>
       </c>
-      <c r="E5" t="s">
+      <c r="G5" t="s">
         <v>35</v>
       </c>
-      <c r="F5" t="s">
+      <c r="H5" t="s">
         <v>36</v>
       </c>
-      <c r="G5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H5" t="s">
-        <v>38</v>
-      </c>
       <c r="I5" t="s">
+        <v>10</v>
+      </c>
+      <c r="J5" t="s">
         <v>11</v>
       </c>
-      <c r="J5" t="s">
-        <v>12</v>
-      </c>
       <c r="K5" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
         <v>39</v>
       </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="E6" t="s">
         <v>40</v>
       </c>
-      <c r="D6" t="s">
+      <c r="F6" t="s">
         <v>41</v>
       </c>
-      <c r="E6" t="s">
+      <c r="G6" t="s">
         <v>42</v>
       </c>
-      <c r="F6" t="s">
+      <c r="H6" t="s">
         <v>43</v>
       </c>
-      <c r="G6" t="s">
-        <v>44</v>
-      </c>
-      <c r="H6" t="s">
-        <v>45</v>
-      </c>
       <c r="I6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J6" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" t="s">
+        <v>19</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" t="s">
         <v>46</v>
       </c>
-      <c r="B7" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" t="s">
-        <v>40</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>47</v>
       </c>
-      <c r="E7" t="s">
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
         <v>48</v>
       </c>
-      <c r="F7" t="s">
-        <v>49</v>
-      </c>
-      <c r="G7" t="s">
-        <v>37</v>
-      </c>
-      <c r="H7" t="s">
-        <v>50</v>
-      </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K7" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
         <v>51</v>
       </c>
-      <c r="B8" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" t="s">
-        <v>40</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>52</v>
       </c>
-      <c r="E8" t="s">
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
         <v>53</v>
       </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-      <c r="G8" t="s">
-        <v>37</v>
-      </c>
-      <c r="H8" t="s">
-        <v>55</v>
-      </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K8" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" t="s">
         <v>56</v>
       </c>
-      <c r="B9" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>57</v>
       </c>
-      <c r="D9" t="s">
+      <c r="F9" t="s">
         <v>58</v>
       </c>
-      <c r="E9" t="s">
+      <c r="G9" t="s">
         <v>59</v>
       </c>
-      <c r="F9" t="s">
+      <c r="H9" t="s">
         <v>60</v>
       </c>
-      <c r="G9" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" t="s">
-        <v>62</v>
-      </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K9" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" t="s">
+        <v>55</v>
+      </c>
+      <c r="D10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" t="s">
         <v>63</v>
       </c>
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>57</v>
-      </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>64</v>
       </c>
-      <c r="E10" t="s">
+      <c r="G10" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" t="s">
         <v>65</v>
       </c>
-      <c r="F10" t="s">
-        <v>66</v>
-      </c>
-      <c r="G10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" t="s">
-        <v>67</v>
-      </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K10" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B11" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" t="s">
+        <v>55</v>
+      </c>
+      <c r="D11" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11" t="s">
         <v>68</v>
       </c>
-      <c r="B11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>69</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>70</v>
       </c>
-      <c r="F11" t="s">
+      <c r="H11" t="s">
         <v>71</v>
       </c>
-      <c r="G11" t="s">
-        <v>72</v>
-      </c>
-      <c r="H11" t="s">
-        <v>73</v>
-      </c>
       <c r="I11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K11" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" t="s">
         <v>74</v>
       </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="E12" t="s">
         <v>75</v>
       </c>
-      <c r="D12" t="s">
+      <c r="F12" t="s">
         <v>76</v>
       </c>
-      <c r="E12" t="s">
+      <c r="G12" t="s">
         <v>77</v>
       </c>
-      <c r="F12" t="s">
+      <c r="H12" t="s">
         <v>78</v>
       </c>
-      <c r="G12" t="s">
-        <v>79</v>
-      </c>
-      <c r="H12" t="s">
-        <v>80</v>
-      </c>
       <c r="I12" t="s">
+        <v>10</v>
+      </c>
+      <c r="J12" t="s">
         <v>11</v>
       </c>
-      <c r="J12" t="s">
-        <v>12</v>
-      </c>
       <c r="K12" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" t="s">
         <v>81</v>
       </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="F13" t="s">
         <v>82</v>
       </c>
-      <c r="E13" t="s">
+      <c r="G13" t="s">
         <v>83</v>
       </c>
-      <c r="F13" t="s">
+      <c r="H13" t="s">
         <v>84</v>
       </c>
-      <c r="G13" t="s">
-        <v>85</v>
-      </c>
-      <c r="H13" t="s">
-        <v>86</v>
-      </c>
       <c r="I13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J13" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K13" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D14" t="s">
+        <v>86</v>
+      </c>
+      <c r="E14" t="s">
         <v>87</v>
       </c>
-      <c r="B14" t="s">
-        <v>21</v>
-      </c>
-      <c r="C14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" t="s">
         <v>88</v>
       </c>
-      <c r="E14" t="s">
+      <c r="H14" t="s">
         <v>89</v>
       </c>
-      <c r="F14" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14" t="s">
-        <v>90</v>
-      </c>
-      <c r="H14" t="s">
-        <v>91</v>
-      </c>
       <c r="I14" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J14" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K14" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C15" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" t="s">
         <v>92</v>
       </c>
-      <c r="B15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>93</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>94</v>
       </c>
-      <c r="F15" t="s">
+      <c r="H15" t="s">
         <v>95</v>
       </c>
-      <c r="G15" t="s">
-        <v>96</v>
-      </c>
-      <c r="H15" t="s">
-        <v>97</v>
-      </c>
       <c r="I15" t="s">
+        <v>13</v>
+      </c>
+      <c r="J15" t="s">
         <v>15</v>
       </c>
-      <c r="J15" t="s">
-        <v>17</v>
-      </c>
       <c r="K15" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
+        <v>96</v>
+      </c>
+      <c r="B16" t="s">
+        <v>19</v>
+      </c>
+      <c r="C16" t="s">
+        <v>97</v>
+      </c>
+      <c r="D16" t="s">
         <v>98</v>
       </c>
-      <c r="B16" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" t="s">
+      <c r="E16" t="s">
+        <v>33</v>
+      </c>
+      <c r="F16" t="s">
         <v>99</v>
       </c>
-      <c r="D16" t="s">
+      <c r="G16" t="s">
         <v>100</v>
       </c>
-      <c r="E16" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" t="s">
+      <c r="H16" t="s">
         <v>101</v>
       </c>
-      <c r="G16" t="s">
-        <v>102</v>
-      </c>
-      <c r="H16" t="s">
-        <v>103</v>
-      </c>
       <c r="I16" t="s">
+        <v>10</v>
+      </c>
+      <c r="J16" t="s">
         <v>11</v>
       </c>
-      <c r="J16" t="s">
-        <v>12</v>
-      </c>
       <c r="K16" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>102</v>
+      </c>
+      <c r="B17" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" t="s">
+        <v>103</v>
+      </c>
+      <c r="E17" t="s">
         <v>104</v>
       </c>
-      <c r="B17" t="s">
-        <v>21</v>
-      </c>
-      <c r="C17" t="s">
-        <v>99</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="F17" t="s">
         <v>105</v>
       </c>
-      <c r="E17" t="s">
+      <c r="G17" t="s">
         <v>106</v>
       </c>
-      <c r="F17" t="s">
+      <c r="H17" t="s">
         <v>107</v>
       </c>
-      <c r="G17" t="s">
-        <v>108</v>
-      </c>
-      <c r="H17" t="s">
-        <v>109</v>
-      </c>
       <c r="I17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J17" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K17" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" t="s">
+        <v>109</v>
+      </c>
+      <c r="E18" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" t="s">
         <v>110</v>
       </c>
-      <c r="B18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C18" t="s">
-        <v>99</v>
-      </c>
-      <c r="D18" t="s">
+      <c r="G18" t="s">
         <v>111</v>
       </c>
-      <c r="E18" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="H18" t="s">
         <v>112</v>
       </c>
-      <c r="G18" t="s">
-        <v>113</v>
-      </c>
-      <c r="H18" t="s">
-        <v>114</v>
-      </c>
       <c r="I18" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J18" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K18" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
+        <v>113</v>
+      </c>
+      <c r="B19" t="s">
+        <v>19</v>
+      </c>
+      <c r="C19" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" t="s">
         <v>115</v>
       </c>
-      <c r="B19" t="s">
-        <v>21</v>
-      </c>
-      <c r="C19" t="s">
-        <v>99</v>
-      </c>
-      <c r="D19" t="s">
+      <c r="F19" t="s">
         <v>116</v>
       </c>
-      <c r="E19" t="s">
+      <c r="G19" t="s">
         <v>117</v>
       </c>
-      <c r="F19" t="s">
+      <c r="H19" t="s">
         <v>118</v>
       </c>
-      <c r="G19" t="s">
-        <v>119</v>
-      </c>
-      <c r="H19" t="s">
-        <v>120</v>
-      </c>
       <c r="I19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J19" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K19" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" t="s">
+        <v>19</v>
+      </c>
+      <c r="C20" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" t="s">
+        <v>120</v>
+      </c>
+      <c r="E20" t="s">
+        <v>104</v>
+      </c>
+      <c r="F20" t="s">
         <v>121</v>
       </c>
-      <c r="B20" t="s">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s">
-        <v>99</v>
-      </c>
-      <c r="D20" t="s">
+      <c r="G20" t="s">
         <v>122</v>
       </c>
-      <c r="E20" t="s">
-        <v>106</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="H20" t="s">
         <v>123</v>
       </c>
-      <c r="G20" t="s">
-        <v>124</v>
-      </c>
-      <c r="H20" t="s">
-        <v>125</v>
-      </c>
       <c r="I20" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" t="s">
         <v>11</v>
       </c>
-      <c r="J20" t="s">
-        <v>12</v>
-      </c>
       <c r="K20" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" t="s">
+        <v>19</v>
+      </c>
+      <c r="C21" t="s">
+        <v>125</v>
+      </c>
+      <c r="D21" t="s">
         <v>126</v>
       </c>
-      <c r="B21" t="s">
-        <v>21</v>
-      </c>
-      <c r="C21" t="s">
+      <c r="E21" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" t="s">
         <v>127</v>
       </c>
-      <c r="D21" t="s">
+      <c r="G21" t="s">
         <v>128</v>
       </c>
-      <c r="E21" t="s">
-        <v>77</v>
-      </c>
-      <c r="F21" t="s">
+      <c r="H21" t="s">
         <v>129</v>
       </c>
-      <c r="G21" t="s">
-        <v>130</v>
-      </c>
-      <c r="H21" t="s">
-        <v>131</v>
-      </c>
       <c r="I21" t="s">
+        <v>10</v>
+      </c>
+      <c r="J21" t="s">
         <v>11</v>
       </c>
-      <c r="J21" t="s">
-        <v>12</v>
-      </c>
       <c r="K21" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B22" t="s">
+        <v>19</v>
+      </c>
+      <c r="C22" t="s">
+        <v>125</v>
+      </c>
+      <c r="D22" t="s">
+        <v>131</v>
+      </c>
+      <c r="E22" t="s">
+        <v>81</v>
+      </c>
+      <c r="F22" t="s">
         <v>132</v>
       </c>
-      <c r="B22" t="s">
-        <v>21</v>
-      </c>
-      <c r="C22" t="s">
-        <v>127</v>
-      </c>
-      <c r="D22" t="s">
+      <c r="G22" t="s">
+        <v>83</v>
+      </c>
+      <c r="H22" t="s">
         <v>133</v>
       </c>
-      <c r="E22" t="s">
-        <v>83</v>
-      </c>
-      <c r="F22" t="s">
-        <v>134</v>
-      </c>
-      <c r="G22" t="s">
-        <v>85</v>
-      </c>
-      <c r="H22" t="s">
-        <v>135</v>
-      </c>
       <c r="I22" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J22" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K22" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>134</v>
+      </c>
+      <c r="B23" t="s">
+        <v>19</v>
+      </c>
+      <c r="C23" t="s">
+        <v>125</v>
+      </c>
+      <c r="D23" t="s">
+        <v>135</v>
+      </c>
+      <c r="E23" t="s">
+        <v>75</v>
+      </c>
+      <c r="F23" t="s">
         <v>136</v>
       </c>
-      <c r="B23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C23" t="s">
-        <v>127</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="G23" t="s">
         <v>137</v>
       </c>
-      <c r="E23" t="s">
-        <v>77</v>
-      </c>
-      <c r="F23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G23" t="s">
-        <v>139</v>
-      </c>
       <c r="H23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I23" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J23" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K23" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>138</v>
+      </c>
+      <c r="B24" t="s">
+        <v>19</v>
+      </c>
+      <c r="C24" t="s">
+        <v>125</v>
+      </c>
+      <c r="D24" t="s">
+        <v>139</v>
+      </c>
+      <c r="E24" t="s">
         <v>140</v>
       </c>
-      <c r="B24" t="s">
-        <v>21</v>
-      </c>
-      <c r="C24" t="s">
-        <v>127</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="F24" t="s">
         <v>141</v>
       </c>
-      <c r="E24" t="s">
-        <v>142</v>
-      </c>
-      <c r="F24" t="s">
-        <v>143</v>
-      </c>
       <c r="G24" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="H24" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I24" t="s">
+        <v>13</v>
+      </c>
+      <c r="J24" t="s">
         <v>15</v>
       </c>
-      <c r="J24" t="s">
-        <v>17</v>
-      </c>
       <c r="K24" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>142</v>
+      </c>
+      <c r="B25" t="s">
+        <v>19</v>
+      </c>
+      <c r="C25" t="s">
+        <v>143</v>
+      </c>
+      <c r="D25" t="s">
         <v>144</v>
       </c>
-      <c r="B25" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="E25" t="s">
+        <v>75</v>
+      </c>
+      <c r="F25" t="s">
         <v>145</v>
       </c>
-      <c r="D25" t="s">
+      <c r="G25" t="s">
         <v>146</v>
       </c>
-      <c r="E25" t="s">
-        <v>77</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="H25" t="s">
         <v>147</v>
       </c>
-      <c r="G25" t="s">
-        <v>148</v>
-      </c>
-      <c r="H25" t="s">
-        <v>149</v>
-      </c>
       <c r="I25" t="s">
+        <v>10</v>
+      </c>
+      <c r="J25" t="s">
         <v>11</v>
       </c>
-      <c r="J25" t="s">
-        <v>12</v>
-      </c>
       <c r="K25" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>148</v>
+      </c>
+      <c r="B26" t="s">
+        <v>19</v>
+      </c>
+      <c r="C26" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" t="s">
+        <v>149</v>
+      </c>
+      <c r="E26" t="s">
+        <v>81</v>
+      </c>
+      <c r="F26" t="s">
         <v>150</v>
       </c>
-      <c r="B26" t="s">
-        <v>21</v>
-      </c>
-      <c r="C26" t="s">
-        <v>145</v>
-      </c>
-      <c r="D26" t="s">
+      <c r="G26" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" t="s">
         <v>151</v>
       </c>
-      <c r="E26" t="s">
-        <v>83</v>
-      </c>
-      <c r="F26" t="s">
-        <v>152</v>
-      </c>
-      <c r="G26" t="s">
-        <v>85</v>
-      </c>
-      <c r="H26" t="s">
-        <v>153</v>
-      </c>
       <c r="I26" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J26" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K26" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>152</v>
+      </c>
+      <c r="B27" t="s">
+        <v>19</v>
+      </c>
+      <c r="C27" t="s">
+        <v>143</v>
+      </c>
+      <c r="D27" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" t="s">
         <v>154</v>
       </c>
-      <c r="B27" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" t="s">
+      <c r="F27" t="s">
         <v>145</v>
       </c>
-      <c r="D27" t="s">
+      <c r="G27" t="s">
         <v>155</v>
       </c>
-      <c r="E27" t="s">
-        <v>156</v>
-      </c>
-      <c r="F27" t="s">
-        <v>147</v>
-      </c>
-      <c r="G27" t="s">
-        <v>157</v>
-      </c>
       <c r="H27" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="I27" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J27" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="K27" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>156</v>
+      </c>
+      <c r="B28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C28" t="s">
+        <v>157</v>
+      </c>
+      <c r="D28" t="s">
         <v>158</v>
       </c>
-      <c r="B28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" t="s">
+      <c r="E28" t="s">
         <v>159</v>
       </c>
-      <c r="D28" t="s">
+      <c r="F28" t="s">
         <v>160</v>
       </c>
-      <c r="E28" t="s">
+      <c r="G28" t="s">
         <v>161</v>
       </c>
-      <c r="F28" t="s">
+      <c r="H28" t="s">
         <v>162</v>
       </c>
-      <c r="G28" t="s">
-        <v>163</v>
-      </c>
-      <c r="H28" t="s">
-        <v>164</v>
-      </c>
       <c r="I28" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J28" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K28" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>163</v>
+      </c>
+      <c r="B29" t="s">
+        <v>19</v>
+      </c>
+      <c r="C29" t="s">
+        <v>157</v>
+      </c>
+      <c r="D29" t="s">
+        <v>164</v>
+      </c>
+      <c r="E29" t="s">
+        <v>81</v>
+      </c>
+      <c r="F29" t="s">
         <v>165</v>
       </c>
-      <c r="B29" t="s">
-        <v>21</v>
-      </c>
-      <c r="C29" t="s">
-        <v>159</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="G29" t="s">
         <v>166</v>
       </c>
-      <c r="E29" t="s">
-        <v>83</v>
-      </c>
-      <c r="F29" t="s">
-        <v>167</v>
-      </c>
-      <c r="G29" t="s">
-        <v>168</v>
-      </c>
       <c r="H29" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="I29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J29" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K29" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>167</v>
+      </c>
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" t="s">
         <v>169</v>
       </c>
-      <c r="B30" t="s">
-        <v>21</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="E30" t="s">
         <v>170</v>
       </c>
-      <c r="D30" t="s">
+      <c r="F30" t="s">
         <v>171</v>
       </c>
-      <c r="E30" t="s">
+      <c r="G30" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" t="s">
         <v>172</v>
       </c>
-      <c r="F30" t="s">
-        <v>173</v>
-      </c>
-      <c r="G30" t="s">
-        <v>37</v>
-      </c>
-      <c r="H30" t="s">
-        <v>174</v>
-      </c>
       <c r="I30" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J30" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K30" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
+        <v>173</v>
+      </c>
+      <c r="B31" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" t="s">
+        <v>174</v>
+      </c>
+      <c r="D31" t="s">
         <v>175</v>
       </c>
-      <c r="B31" t="s">
-        <v>21</v>
-      </c>
-      <c r="C31" t="s">
+      <c r="E31" t="s">
         <v>176</v>
       </c>
-      <c r="D31" t="s">
+      <c r="F31" t="s">
         <v>177</v>
       </c>
-      <c r="E31" t="s">
+      <c r="G31" t="s">
         <v>178</v>
       </c>
-      <c r="F31" t="s">
-        <v>179</v>
-      </c>
-      <c r="G31" t="s">
-        <v>180</v>
-      </c>
       <c r="H31" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I31" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J31" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K31" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
+        <v>179</v>
+      </c>
+      <c r="B32" t="s">
+        <v>19</v>
+      </c>
+      <c r="C32" t="s">
+        <v>180</v>
+      </c>
+      <c r="D32" t="s">
         <v>181</v>
       </c>
-      <c r="B32" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" t="s">
+      <c r="E32" t="s">
         <v>182</v>
       </c>
-      <c r="D32" t="s">
+      <c r="F32" t="s">
         <v>183</v>
       </c>
-      <c r="E32" t="s">
+      <c r="G32" t="s">
         <v>184</v>
       </c>
-      <c r="F32" t="s">
+      <c r="H32" t="s">
         <v>185</v>
       </c>
-      <c r="G32" t="s">
-        <v>186</v>
-      </c>
-      <c r="H32" t="s">
-        <v>187</v>
-      </c>
       <c r="I32" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J32" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K32" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>186</v>
+      </c>
+      <c r="B33" t="s">
+        <v>19</v>
+      </c>
+      <c r="C33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" t="s">
         <v>188</v>
       </c>
-      <c r="B33" t="s">
-        <v>21</v>
-      </c>
-      <c r="C33" t="s">
+      <c r="E33" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" t="s">
         <v>189</v>
       </c>
-      <c r="D33" t="s">
+      <c r="G33" t="s">
         <v>190</v>
       </c>
-      <c r="E33" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="H33" t="s">
         <v>191</v>
       </c>
-      <c r="G33" t="s">
-        <v>192</v>
-      </c>
-      <c r="H33" t="s">
-        <v>193</v>
-      </c>
       <c r="I33" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J33" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K33" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
+        <v>192</v>
+      </c>
+      <c r="B34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C34" t="s">
+        <v>193</v>
+      </c>
+      <c r="D34" t="s">
         <v>194</v>
       </c>
-      <c r="B34" t="s">
-        <v>21</v>
-      </c>
-      <c r="C34" t="s">
+      <c r="E34" t="s">
         <v>195</v>
       </c>
-      <c r="D34" t="s">
+      <c r="F34" t="s">
         <v>196</v>
       </c>
-      <c r="E34" t="s">
+      <c r="G34" t="s">
         <v>197</v>
       </c>
-      <c r="F34" t="s">
+      <c r="H34" t="s">
         <v>198</v>
       </c>
-      <c r="G34" t="s">
-        <v>199</v>
-      </c>
-      <c r="H34" t="s">
-        <v>200</v>
-      </c>
       <c r="I34" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J34" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K34" t="s">
-        <v>13</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2196,6 +2193,11 @@
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K1:K1048576" xr:uid="{03B169BB-69B9-403C-9F48-BDF6AF8C0FD7}">
+      <formula1>"Passed,Failed,Blocked"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>